--- a/syllabus/再構築計画.xlsx
+++ b/syllabus/再構築計画.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Napier/Dropbox/Git/psychometrtics_syllabus/syllabus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/napier/Dropbox/Git/psychometrtics_syllabus/syllabus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AFBB1D-59A4-CD4D-B5E0-64A719648C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47B4C718-4FEA-944D-8941-34DB1276EDC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26700" xr2:uid="{5A83AC4D-FD37-C349-BFA0-5F3B00CCA608}"/>
+    <workbookView xWindow="25060" yWindow="1480" windowWidth="51200" windowHeight="26600" xr2:uid="{5A83AC4D-FD37-C349-BFA0-5F3B00CCA608}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="137">
   <si>
     <t>16 確率と統計的推論</t>
   </si>
@@ -584,10 +584,6 @@
     <rPh sb="8" eb="10">
       <t xml:space="preserve">カクリツ </t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>26　ベイズ推測の基礎</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -758,6 +754,23 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t xml:space="preserve">セイキブンプノボスウスイテイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17 推論と判断</t>
+    <rPh sb="3" eb="5">
+      <t xml:space="preserve">スイロントイシケッテイ </t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">ハンダン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>26　ベイズ推測の実際</t>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">ベイズスイソクノジッサイ </t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1167,7 +1180,7 @@
         <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1224,7 +1237,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="C7" t="s">
         <v>64</v>
@@ -1271,7 +1284,7 @@
         <v>72</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1290,7 +1303,7 @@
         <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1301,7 +1314,7 @@
         <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1438,7 +1451,7 @@
         <v>88</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1446,7 +1459,7 @@
         <v>89</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1646,7 +1659,7 @@
         <v>39</v>
       </c>
       <c r="B50" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1654,12 +1667,12 @@
         <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="B52" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1667,22 +1680,22 @@
         <v>41</v>
       </c>
       <c r="B53" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="B54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="B55" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="B56" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1690,7 +1703,7 @@
         <v>42</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1698,7 +1711,7 @@
         <v>43</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1706,7 +1719,7 @@
         <v>44</v>
       </c>
       <c r="B59" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1714,7 +1727,7 @@
         <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1722,18 +1735,18 @@
         <v>46</v>
       </c>
       <c r="B61" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C61" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="B62" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C62" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1741,18 +1754,18 @@
         <v>47</v>
       </c>
       <c r="B63" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C63" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="B64" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C64" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1760,12 +1773,12 @@
         <v>48</v>
       </c>
       <c r="B65" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="B66" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1773,7 +1786,7 @@
         <v>49</v>
       </c>
       <c r="B67" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" spans="1:2">

--- a/syllabus/再構築計画.xlsx
+++ b/syllabus/再構築計画.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11114"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/napier/Dropbox/Git/psychometrtics_syllabus/syllabus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47B4C718-4FEA-944D-8941-34DB1276EDC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE0A7EF-7F1D-9748-BDDB-2F12A3B642E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25060" yWindow="1480" windowWidth="51200" windowHeight="26600" xr2:uid="{5A83AC4D-FD37-C349-BFA0-5F3B00CCA608}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" xr2:uid="{5A83AC4D-FD37-C349-BFA0-5F3B00CCA608}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="130">
   <si>
     <t>16 確率と統計的推論</t>
   </si>
@@ -566,123 +566,9 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>25.1　二次元の確率変数</t>
-    <rPh sb="5" eb="8">
-      <t xml:space="preserve">ニジゲン </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>25.2　ベイズの定理</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>25.3　推論と確率</t>
-    <rPh sb="5" eb="7">
-      <t xml:space="preserve">スイロントカクリツ </t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t xml:space="preserve">カクリツ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>26.1　事前分布と事後分布</t>
     <rPh sb="5" eb="9">
       <t xml:space="preserve">ジゼンブンプ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>26.2　尤度</t>
-    <rPh sb="5" eb="7">
-      <t xml:space="preserve">ユウド </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>26.3　周辺ゆうど</t>
-    <rPh sb="5" eb="7">
-      <t xml:space="preserve">シュウヘンユウド </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>26.4　MCMC法</t>
-    <rPh sb="9" eb="10">
-      <t xml:space="preserve">ホウ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>27　ベイズ法による母数の推定</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>27.1　ベルヌーイ分布の母数推定</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>27.2　事前分布と尤度の折衷</t>
-    <rPh sb="5" eb="9">
-      <t xml:space="preserve">ジゼンブンプ </t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t xml:space="preserve">ユウドノ </t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t xml:space="preserve">セッチュウ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>27.3　事後分布を代表する数字</t>
-    <rPh sb="5" eb="9">
-      <t xml:space="preserve">ジゴブンプヲダイヒョウスルスウジ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>28　ベイズ法による回帰分析</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>28.1　回帰分析と尤度</t>
-    <rPh sb="5" eb="9">
-      <t xml:space="preserve">カイキブンセキトユウド </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>28.2　要因計画と推定</t>
-    <rPh sb="5" eb="9">
-      <t xml:space="preserve">ヨウインケイカクトスイテイ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>29　Rによるベイズ推測</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>29.1　回帰分析のベイズ推定</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>29.2　モデルを用いた予測</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>29.4　MCMCを使った分析のレポート</t>
-    <rPh sb="13" eb="15">
-      <t xml:space="preserve">ブンセキノレポート </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>29.3　分散分析モデル</t>
-    <rPh sb="5" eb="9">
-      <t>json</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -741,23 +627,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>28.3　ベイズ法による判断；モデル比較</t>
-    <rPh sb="8" eb="9">
-      <t xml:space="preserve">ベイズホウニヨルハンダン </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>27.4　正規分布の母数推定</t>
-    <rPh sb="5" eb="7">
-      <t xml:space="preserve">セイキ </t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t xml:space="preserve">セイキブンプノボスウスイテイ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>17 推論と判断</t>
     <rPh sb="3" eb="5">
       <t xml:space="preserve">スイロントイシケッテイ </t>
@@ -772,6 +641,106 @@
     <rPh sb="6" eb="8">
       <t xml:space="preserve">ベイズスイソクノジッサイ </t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>25.1　条件付き確率，周辺確率，独立</t>
+    <rPh sb="5" eb="8">
+      <t xml:space="preserve">ジョウケンツキカクリツ </t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t xml:space="preserve">シュウヘンカクリツ </t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t xml:space="preserve">ドクリツ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>25.2　ベイズの定理の数学的意味</t>
+    <rPh sb="12" eb="17">
+      <t xml:space="preserve">スウガクテキイミ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>25.3　ベイズの定理の実際の意味</t>
+    <rPh sb="12" eb="14">
+      <t xml:space="preserve">ジッサイノイミ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>26.2　事後分布を代表する数字</t>
+    <rPh sb="5" eb="9">
+      <t xml:space="preserve">ジゴブンプ </t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t xml:space="preserve">ダイヒョウスルスウジ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>26.3　事前分布の活用・・・釘のコイントスの例を用いて</t>
+    <rPh sb="5" eb="9">
+      <t xml:space="preserve">ジゼンブンプノカツヨウ </t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t xml:space="preserve">クギノコイントスノレイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>27.ベイズ推定の利用</t>
+    <rPh sb="9" eb="11">
+      <t xml:space="preserve">リヨウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>27.2　JASPによるベイズ推定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>27.3　JASPによる平均の比較</t>
+    <rPh sb="12" eb="14">
+      <t xml:space="preserve">ヘイキン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>27.1　ベイズ法と帰無仮説検定</t>
+    <rPh sb="10" eb="16">
+      <t xml:space="preserve">キムカセツケンテイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>28.ベイズ推定の技術</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>28.1　乱数による近似計算</t>
+    <rPh sb="5" eb="7">
+      <t xml:space="preserve">ランスウニヨルボ </t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t xml:space="preserve">キンジ </t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t xml:space="preserve">ケイサン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>28.2　回帰分析の最尤推定とベイズ推定</t>
+    <rPh sb="5" eb="9">
+      <t xml:space="preserve">カイキブンセキノサイユウスイテイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>27.2　ベイズ法によるモデル比較</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -841,7 +810,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -850,6 +819,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1180,7 +1152,7 @@
         <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1237,7 +1209,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="C7" t="s">
         <v>64</v>
@@ -1284,7 +1256,7 @@
         <v>72</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1303,7 +1275,7 @@
         <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1314,7 +1286,7 @@
         <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1451,7 +1423,7 @@
         <v>88</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1459,7 +1431,7 @@
         <v>89</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1635,7 +1607,7 @@
         <v>36</v>
       </c>
       <c r="B47" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1643,129 +1615,114 @@
         <v>37</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>38</v>
       </c>
       <c r="B49" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>39</v>
       </c>
       <c r="B50" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="B52" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53" t="s">
         <v>41</v>
       </c>
       <c r="B53" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="B54" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="B55" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="B56" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>42</v>
       </c>
-      <c r="B57" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
+      <c r="B57" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>43</v>
       </c>
-      <c r="B58" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>44</v>
       </c>
       <c r="B59" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>46</v>
       </c>
       <c r="B61" t="s">
-        <v>120</v>
-      </c>
-      <c r="C61" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
       <c r="B62" t="s">
-        <v>121</v>
-      </c>
-      <c r="C62" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
       <c r="A63" t="s">
         <v>47</v>
       </c>
       <c r="B63" t="s">
-        <v>122</v>
-      </c>
-      <c r="C63" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
       <c r="B64" t="s">
-        <v>123</v>
-      </c>
-      <c r="C64" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1773,12 +1730,12 @@
         <v>48</v>
       </c>
       <c r="B65" t="s">
-        <v>124</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="B66" t="s">
-        <v>126</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1786,7 +1743,7 @@
         <v>49</v>
       </c>
       <c r="B67" t="s">
-        <v>125</v>
+        <v>59</v>
       </c>
     </row>
     <row r="68" spans="1:2">

--- a/syllabus/再構築計画.xlsx
+++ b/syllabus/再構築計画.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/napier/Dropbox/Git/psychometrtics_syllabus/syllabus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE0A7EF-7F1D-9748-BDDB-2F12A3B642E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35C3CDE-B275-914B-8330-A0B8E817BA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" xr2:uid="{5A83AC4D-FD37-C349-BFA0-5F3B00CCA608}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="1" xr2:uid="{5A83AC4D-FD37-C349-BFA0-5F3B00CCA608}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="2021年後期" sheetId="1" r:id="rId1"/>
+    <sheet name="2022年通年" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="285">
   <si>
     <t>16 確率と統計的推論</t>
   </si>
@@ -743,12 +744,1100 @@
     <t>27.2　ベイズ法によるモデル比較</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>見出し</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ミダシ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Section1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Section2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Section3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Section4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>心理学と統計法</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">シンリガクトトウケイホウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>心理学とはどういう学問か</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">シンリガクトハドウイウガクモンカ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>二つの流派</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">フタツノリュウハ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>近代科学の特徴</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">キンダイカガクノトクチョウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電子計算機のイロハ</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">デンシケイサンキノイロハ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンピュータ基礎</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンピュータ史</t>
+    <rPh sb="6" eb="7">
+      <t xml:space="preserve">シ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報の単位</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ジョウホウノタンイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファイルの場所</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>再現性のある研究実践</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">サイゲンセイノアルジッケン </t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t xml:space="preserve">ケンキュウジッセン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>数値データの種類</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">スウチデータノシュルイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データと変数</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変数の分類</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ヘンスウノブンルイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>尺度水準による分類</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">シャクドスイジュン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>可視化</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">カシカ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>記述統計量</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">キジュツトウケイリョウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中心化傾向の指標</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">チュウシンカケイコウノシヒョウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>散らばりの指標</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">チラバリノシヒョウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相対的位置/標準化</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">ソウタイテキイチ </t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t xml:space="preserve">ヒョウジュンカ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変数間関係の指標</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ヘンスウイカンカンケイノ </t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">アイダ </t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t xml:space="preserve">カンケイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rを使ってみる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rstudioとは</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rmarkdownとは</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tidyデータとは</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ggplot2とは</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>古典的テスト理論</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">コテンテキテストリロン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストと心理学</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>測定のモデル</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ソクテイノモデル </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誤差と正規分布</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ゴサノキホンテキセイシツ </t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t xml:space="preserve">セイキブンプ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストの平均値</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>信頼性と妥当性</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">シンライセイトダトウセイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確率分布</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">カクリツブンプ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確率の二つの意味</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">カクリツノフタツノイミ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>二項分布</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">ニコウブンプ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正規分布</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">セイキブンプ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正規分布の形</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">セイキブンプノカタチ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正規分布の関数</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">セイキブンプノカンスウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>連続確率分布</t>
+    <rPh sb="0" eb="6">
+      <t xml:space="preserve">レンゾクカクリツブンプ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>標準正規分布</t>
+    <rPh sb="0" eb="6">
+      <t xml:space="preserve">ヒョウジュンセイキブンプ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>線形モデルの基礎</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">センケイモデルノキソ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相関係数とモデル</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">ソウカンケイスウトモデル </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>予測と線形モデル</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ヨソクトセンケイモデル </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最小二乗法</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">サイショウニジョウホウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残差と決定係数</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ザンサ </t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t xml:space="preserve">ケッテイケイスウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重回帰分析</t>
+    <rPh sb="0" eb="5">
+      <t>ジュウカイキブンセk</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重回帰分析</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">ジュウカイキブンセキ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>偏回帰係数</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ヘン </t>
+    </rPh>
+    <rPh sb="1" eb="5">
+      <t xml:space="preserve">カイキケイスウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>標準化偏回帰係数</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">ヒョウジュンカ </t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t xml:space="preserve">ヘン </t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t xml:space="preserve">カイキケイスウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>多重共線性</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">タジュウキョウセンセイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外部データの読み込み</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ガイブデータノヨミコミ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>散布図の描画</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>線形回帰の実行</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">センケイ </t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t xml:space="preserve">カイキ </t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t xml:space="preserve">ジッコウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残差のプロット</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ザンサ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重回帰分析の実行</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">ジュウカイキブンセキ </t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">ジッコウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rを使った回帰分析</t>
+    <rPh sb="1" eb="2">
+      <t>ヲ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t xml:space="preserve">カイキ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実験計画法1</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">ジッケンケイカクホウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RCT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要因と水準</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ヨウイン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誤差と効果</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ゴサトコウカ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平均差の効果</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">ヘイキンサ </t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t xml:space="preserve">コウカ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実験計画法2</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ジッケンケイカクホウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイン行列</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>二要因モデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平方和の分解</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">ヘイホウワノブンカイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>交互作用</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">コウゴサヨウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実験計画法3</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">ジッケンケイカクホウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Within計画</t>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">ケイカク </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モデルと誤差</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>間と内の違い</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">アイダ </t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">ナイ </t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t xml:space="preserve">チガイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誤差の分布，個人差の分布</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ゴサノブンプ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前期のテスト</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ゼンキノテスト </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確率と統計的推論</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">カクリツトトウケイテキスイロン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>母集団と標本</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">ボシュウダントヒョウホン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>母集団分布とモデル</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">ボシュウダンブンプ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>標本分布と標本誤差</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ヒョウホンブンプ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>推論と判断</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">スイロントハンダン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不偏推定量/不偏分散</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">フヘンスイテイリョウ </t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">フヘン </t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t xml:space="preserve">ブンサン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>点推定と区間推定</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">テン </t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t xml:space="preserve">スイテイ </t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t xml:space="preserve">クカン </t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">スイテイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>標準正規分布の利用</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ヒョウジュンセイキブンプノリヨウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>標本だけを使った推定</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ヒョウホンダケヲツカッタスイテイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>推定と検定</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">スイテイトケンテイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>帰無仮説検定</t>
+    <rPh sb="0" eb="6">
+      <t xml:space="preserve">キムカセツケンテイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>帰無仮説検定とその手順</t>
+    <rPh sb="0" eb="6">
+      <t xml:space="preserve">キムカセツケンテイトソノテジュン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>有意水準</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">ユウイスイジュン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一つの平均値の検定</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ヒトツノヘイキンチ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相関係数の検定</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">ソウカンケイスウノケンテイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>帰無仮説検定の注意点</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">キムカセツケンテイノチュウイテン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>結果の報告</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ケッカノホウコク </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>統計的に有意とは</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">トウケイテキニユウイトハ </t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t xml:space="preserve">ユウイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一つの平均値の検定（母集団未知）</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ヒトツノヘイキンチノケンテイ </t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t xml:space="preserve">ミチ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>二種類の間違い</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ニシュルイノマチガイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>二群の平均値差</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ニグン </t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t xml:space="preserve">サ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Within2水準</t>
+    <rPh sb="7" eb="9">
+      <t xml:space="preserve">スイジュン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Between2水準</t>
+    <rPh sb="8" eb="10">
+      <t xml:space="preserve">スイジュン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rによる一要因W2</t>
+    <rPh sb="4" eb="7">
+      <t xml:space="preserve">イチヨウイン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rによる一要因B2</t>
+    <rPh sb="4" eb="7">
+      <t xml:space="preserve">イチヨウイン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要因計画と平均値差の検定</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">ヨウインケイカクトヘイキンチ </t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t xml:space="preserve">サ </t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t xml:space="preserve">ケンテイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要因計画と推定</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">ヨウインケイカクトスイテイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一要因Between</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">イチヨウイン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>事後の検定</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ジゴノケンテイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>二要因デザイン</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">ニヨウイン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rによる分散分析</t>
+    <rPh sb="4" eb="8">
+      <t xml:space="preserve">ブンサンブンセキ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一要因B3</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">イチヨウイン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>二要因B2x2</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ニヨウイン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一要因Within3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確率分布とデータの関係</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">カクリツブンプトデータノカンケイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確率関数と尤度関数</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">カクリツカンスウトユウドカンスウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最尤推定</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">サイユウスイテイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対数尤度関数</t>
+    <rPh sb="0" eb="6">
+      <t xml:space="preserve">タイスウユウドカンスウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正規分布の尤度関数</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">セイキブンプノユウドカンスウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回帰分析の最尤推定</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">カイキブンセキノサイユウスイテイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回帰分析と後座分布</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">カイキブンセキトゴザブンプ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確率モデルへ</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">カクリツモデル </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確率モデルと最尤推定</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">カクリツモデルトサイユウスイテイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベイズ推定の基礎</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>二次元の確率変数</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">ニジゲン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベイズの定理の意味</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベイズの定理を使った推論</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベイズ推定の実際</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ベイズスイテイノジッサイ </t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">ジッサイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>事前分布と事後分布</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">ジゼンブンプ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>事後分布を代表する数字</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">ジゴブンプヲダイヒョウスルスウジ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>事前分布の影響</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ジゼンブンプノエイキョウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベイズ推定と判断</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベイズとNHST</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>区間による判定</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">クカンニヨルハンテイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベイズファクター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JASPによるベイズ推定の実践</t>
+    <rPh sb="13" eb="15">
+      <t xml:space="preserve">ジッセン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベイズ推定の方法</t>
+    <rPh sb="0" eb="1">
+      <t>トNHST</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JASPの導入</t>
+    <rPh sb="5" eb="7">
+      <t xml:space="preserve">ドウニュウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JASPによる回帰</t>
+    <rPh sb="7" eb="9">
+      <t xml:space="preserve">カイキ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JASPによる平均の比較</t>
+    <rPh sb="7" eb="9">
+      <t xml:space="preserve">ヘイキン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まとめ・Rによるベイズ推定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後期の試験</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">コウキノシケン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回帰分析のベイズ推定</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">カイキブンセキノベイズスイテイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モデルを用いた予測</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MCMCを使った分析のレポート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rとは</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ggplot2による可視化</t>
+    <rPh sb="10" eb="13">
+      <t xml:space="preserve">カシカ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>統計環境Rの利用</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">トウケイカンキョウ </t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">リヨウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>統計環境Rの導入</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">トウケイカンキョウ </t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">ドウニュウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rによるベイズ推定</t>
+    <rPh sb="1" eb="4">
+      <t>ニヨル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前期の試験</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ゼンキノテスト </t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t xml:space="preserve">シケン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相関と因果</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ソウカントインガ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>因果関係</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">インガカンケイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>単回帰分析</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">タンカイキブンセキ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>疑似相関</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">ギジソウカン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>交絡</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">コウラク </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>測定の基礎</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ソクテイノキソ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>古典的テスト理論</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">コテンテキテストリオルン </t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">リロン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -787,6 +1876,21 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -810,7 +1914,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -822,6 +1926,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1800,4 +2913,1103 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAD22543-E06A-6249-A917-871CAD278F17}">
+  <dimension ref="A1:O31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <cols>
+    <col min="2" max="7" width="21" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="B1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" t="s">
+        <v>131</v>
+      </c>
+      <c r="L1" t="s">
+        <v>132</v>
+      </c>
+      <c r="M1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K2" t="s">
+        <v>136</v>
+      </c>
+      <c r="L2" t="s">
+        <v>137</v>
+      </c>
+      <c r="M2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3" t="s">
+        <v>145</v>
+      </c>
+      <c r="K3" t="s">
+        <v>146</v>
+      </c>
+      <c r="L3" t="s">
+        <v>147</v>
+      </c>
+      <c r="M3" t="s">
+        <v>148</v>
+      </c>
+      <c r="N3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="21">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F4" t="s">
+        <v>149</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4" t="s">
+        <v>274</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="L4" t="s">
+        <v>156</v>
+      </c>
+      <c r="M4" t="s">
+        <v>143</v>
+      </c>
+      <c r="N4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" t="s">
+        <v>154</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5" t="s">
+        <v>273</v>
+      </c>
+      <c r="K5" t="s">
+        <v>157</v>
+      </c>
+      <c r="L5" t="s">
+        <v>184</v>
+      </c>
+      <c r="M5" t="s">
+        <v>158</v>
+      </c>
+      <c r="N5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="21">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6" t="s">
+        <v>283</v>
+      </c>
+      <c r="K6" t="s">
+        <v>284</v>
+      </c>
+      <c r="L6" t="s">
+        <v>162</v>
+      </c>
+      <c r="M6" t="s">
+        <v>164</v>
+      </c>
+      <c r="N6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G7" t="s">
+        <v>165</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7" t="s">
+        <v>277</v>
+      </c>
+      <c r="K7" t="s">
+        <v>278</v>
+      </c>
+      <c r="L7" t="s">
+        <v>281</v>
+      </c>
+      <c r="M7" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D8" t="s">
+        <v>166</v>
+      </c>
+      <c r="E8" t="s">
+        <v>168</v>
+      </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
+      <c r="J8" t="s">
+        <v>279</v>
+      </c>
+      <c r="K8" t="s">
+        <v>280</v>
+      </c>
+      <c r="L8" t="s">
+        <v>176</v>
+      </c>
+      <c r="M8" t="s">
+        <v>177</v>
+      </c>
+      <c r="N8" t="s">
+        <v>178</v>
+      </c>
+      <c r="O8" s="5"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
+      <c r="J9" t="s">
+        <v>180</v>
+      </c>
+      <c r="K9" t="s">
+        <v>179</v>
+      </c>
+      <c r="L9" t="s">
+        <v>181</v>
+      </c>
+      <c r="M9" t="s">
+        <v>182</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" t="s">
+        <v>176</v>
+      </c>
+      <c r="E10" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10" t="s">
+        <v>178</v>
+      </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
+      <c r="J10" t="s">
+        <v>189</v>
+      </c>
+      <c r="K10" t="s">
+        <v>185</v>
+      </c>
+      <c r="L10" t="s">
+        <v>186</v>
+      </c>
+      <c r="M10" t="s">
+        <v>187</v>
+      </c>
+      <c r="N10" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F11" t="s">
+        <v>183</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11" t="s">
+        <v>166</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="L11" t="s">
+        <v>166</v>
+      </c>
+      <c r="M11" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" t="s">
+        <v>185</v>
+      </c>
+      <c r="E12" t="s">
+        <v>186</v>
+      </c>
+      <c r="F12" t="s">
+        <v>187</v>
+      </c>
+      <c r="G12" t="s">
+        <v>188</v>
+      </c>
+      <c r="I12">
+        <v>11</v>
+      </c>
+      <c r="J12" t="s">
+        <v>169</v>
+      </c>
+      <c r="K12" t="s">
+        <v>170</v>
+      </c>
+      <c r="L12" t="s">
+        <v>171</v>
+      </c>
+      <c r="M12" t="s">
+        <v>172</v>
+      </c>
+      <c r="N12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" t="s">
+        <v>191</v>
+      </c>
+      <c r="D13" t="s">
+        <v>192</v>
+      </c>
+      <c r="E13" t="s">
+        <v>193</v>
+      </c>
+      <c r="F13" t="s">
+        <v>194</v>
+      </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
+      <c r="J13" t="s">
+        <v>190</v>
+      </c>
+      <c r="K13" t="s">
+        <v>191</v>
+      </c>
+      <c r="L13" t="s">
+        <v>192</v>
+      </c>
+      <c r="M13" t="s">
+        <v>193</v>
+      </c>
+      <c r="N13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D14" t="s">
+        <v>197</v>
+      </c>
+      <c r="E14" t="s">
+        <v>198</v>
+      </c>
+      <c r="F14" t="s">
+        <v>199</v>
+      </c>
+      <c r="I14">
+        <v>13</v>
+      </c>
+      <c r="J14" t="s">
+        <v>195</v>
+      </c>
+      <c r="K14" t="s">
+        <v>196</v>
+      </c>
+      <c r="L14" t="s">
+        <v>197</v>
+      </c>
+      <c r="M14" t="s">
+        <v>198</v>
+      </c>
+      <c r="N14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>200</v>
+      </c>
+      <c r="C15" t="s">
+        <v>201</v>
+      </c>
+      <c r="D15" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" t="s">
+        <v>203</v>
+      </c>
+      <c r="F15" t="s">
+        <v>204</v>
+      </c>
+      <c r="I15">
+        <v>14</v>
+      </c>
+      <c r="J15" t="s">
+        <v>200</v>
+      </c>
+      <c r="K15" t="s">
+        <v>201</v>
+      </c>
+      <c r="L15" t="s">
+        <v>202</v>
+      </c>
+      <c r="M15" t="s">
+        <v>203</v>
+      </c>
+      <c r="N15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>205</v>
+      </c>
+      <c r="I16">
+        <v>15</v>
+      </c>
+      <c r="J16" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>206</v>
+      </c>
+      <c r="C17" t="s">
+        <v>207</v>
+      </c>
+      <c r="D17" t="s">
+        <v>208</v>
+      </c>
+      <c r="E17" t="s">
+        <v>209</v>
+      </c>
+      <c r="I17">
+        <v>16</v>
+      </c>
+      <c r="J17" t="s">
+        <v>206</v>
+      </c>
+      <c r="K17" t="s">
+        <v>207</v>
+      </c>
+      <c r="L17" t="s">
+        <v>208</v>
+      </c>
+      <c r="M17" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>210</v>
+      </c>
+      <c r="C18" t="s">
+        <v>211</v>
+      </c>
+      <c r="D18" t="s">
+        <v>212</v>
+      </c>
+      <c r="E18" t="s">
+        <v>213</v>
+      </c>
+      <c r="F18" t="s">
+        <v>214</v>
+      </c>
+      <c r="G18" t="s">
+        <v>215</v>
+      </c>
+      <c r="I18">
+        <v>17</v>
+      </c>
+      <c r="J18" t="s">
+        <v>210</v>
+      </c>
+      <c r="K18" t="s">
+        <v>211</v>
+      </c>
+      <c r="L18" t="s">
+        <v>212</v>
+      </c>
+      <c r="M18" t="s">
+        <v>213</v>
+      </c>
+      <c r="N18" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>216</v>
+      </c>
+      <c r="C19" t="s">
+        <v>217</v>
+      </c>
+      <c r="D19" t="s">
+        <v>218</v>
+      </c>
+      <c r="E19" t="s">
+        <v>219</v>
+      </c>
+      <c r="F19" t="s">
+        <v>224</v>
+      </c>
+      <c r="G19" t="s">
+        <v>220</v>
+      </c>
+      <c r="I19">
+        <v>18</v>
+      </c>
+      <c r="J19" t="s">
+        <v>216</v>
+      </c>
+      <c r="K19" t="s">
+        <v>217</v>
+      </c>
+      <c r="L19" t="s">
+        <v>218</v>
+      </c>
+      <c r="M19" t="s">
+        <v>219</v>
+      </c>
+      <c r="N19" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>221</v>
+      </c>
+      <c r="C20" t="s">
+        <v>222</v>
+      </c>
+      <c r="D20" t="s">
+        <v>223</v>
+      </c>
+      <c r="E20" t="s">
+        <v>225</v>
+      </c>
+      <c r="I20">
+        <v>19</v>
+      </c>
+      <c r="J20" t="s">
+        <v>221</v>
+      </c>
+      <c r="K20" t="s">
+        <v>222</v>
+      </c>
+      <c r="L20" t="s">
+        <v>223</v>
+      </c>
+      <c r="M20" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>226</v>
+      </c>
+      <c r="C21" t="s">
+        <v>227</v>
+      </c>
+      <c r="D21" t="s">
+        <v>228</v>
+      </c>
+      <c r="E21" t="s">
+        <v>229</v>
+      </c>
+      <c r="F21" t="s">
+        <v>230</v>
+      </c>
+      <c r="I21">
+        <v>20</v>
+      </c>
+      <c r="J21" t="s">
+        <v>226</v>
+      </c>
+      <c r="K21" t="s">
+        <v>227</v>
+      </c>
+      <c r="L21" t="s">
+        <v>228</v>
+      </c>
+      <c r="M21" t="s">
+        <v>229</v>
+      </c>
+      <c r="N21" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C22" t="s">
+        <v>232</v>
+      </c>
+      <c r="D22" t="s">
+        <v>233</v>
+      </c>
+      <c r="E22" t="s">
+        <v>234</v>
+      </c>
+      <c r="F22" t="s">
+        <v>235</v>
+      </c>
+      <c r="I22">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>231</v>
+      </c>
+      <c r="K22" t="s">
+        <v>232</v>
+      </c>
+      <c r="L22" t="s">
+        <v>233</v>
+      </c>
+      <c r="M22" t="s">
+        <v>234</v>
+      </c>
+      <c r="N22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>236</v>
+      </c>
+      <c r="C23" t="s">
+        <v>237</v>
+      </c>
+      <c r="D23" t="s">
+        <v>238</v>
+      </c>
+      <c r="E23" t="s">
+        <v>239</v>
+      </c>
+      <c r="I23">
+        <v>22</v>
+      </c>
+      <c r="J23" t="s">
+        <v>236</v>
+      </c>
+      <c r="K23" t="s">
+        <v>237</v>
+      </c>
+      <c r="L23" t="s">
+        <v>238</v>
+      </c>
+      <c r="M23" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>240</v>
+      </c>
+      <c r="C24" t="s">
+        <v>241</v>
+      </c>
+      <c r="D24" t="s">
+        <v>242</v>
+      </c>
+      <c r="E24" t="s">
+        <v>243</v>
+      </c>
+      <c r="F24" t="s">
+        <v>244</v>
+      </c>
+      <c r="I24">
+        <v>23</v>
+      </c>
+      <c r="J24" t="s">
+        <v>240</v>
+      </c>
+      <c r="K24" t="s">
+        <v>241</v>
+      </c>
+      <c r="L24" t="s">
+        <v>242</v>
+      </c>
+      <c r="M24" t="s">
+        <v>243</v>
+      </c>
+      <c r="N24" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>245</v>
+      </c>
+      <c r="C25" t="s">
+        <v>246</v>
+      </c>
+      <c r="D25" t="s">
+        <v>247</v>
+      </c>
+      <c r="E25" t="s">
+        <v>248</v>
+      </c>
+      <c r="I25">
+        <v>24</v>
+      </c>
+      <c r="J25" t="s">
+        <v>245</v>
+      </c>
+      <c r="K25" t="s">
+        <v>246</v>
+      </c>
+      <c r="L25" t="s">
+        <v>247</v>
+      </c>
+      <c r="M25" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C26" t="s">
+        <v>250</v>
+      </c>
+      <c r="D26" t="s">
+        <v>251</v>
+      </c>
+      <c r="E26" t="s">
+        <v>252</v>
+      </c>
+      <c r="I26">
+        <v>25</v>
+      </c>
+      <c r="J26" t="s">
+        <v>249</v>
+      </c>
+      <c r="K26" t="s">
+        <v>250</v>
+      </c>
+      <c r="L26" t="s">
+        <v>251</v>
+      </c>
+      <c r="M26" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>253</v>
+      </c>
+      <c r="C27" t="s">
+        <v>254</v>
+      </c>
+      <c r="D27" t="s">
+        <v>255</v>
+      </c>
+      <c r="E27" t="s">
+        <v>256</v>
+      </c>
+      <c r="I27">
+        <v>26</v>
+      </c>
+      <c r="J27" t="s">
+        <v>253</v>
+      </c>
+      <c r="K27" t="s">
+        <v>254</v>
+      </c>
+      <c r="L27" t="s">
+        <v>255</v>
+      </c>
+      <c r="M27" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>257</v>
+      </c>
+      <c r="C28" t="s">
+        <v>258</v>
+      </c>
+      <c r="D28" t="s">
+        <v>259</v>
+      </c>
+      <c r="E28" t="s">
+        <v>260</v>
+      </c>
+      <c r="I28">
+        <v>27</v>
+      </c>
+      <c r="J28" t="s">
+        <v>257</v>
+      </c>
+      <c r="K28" t="s">
+        <v>258</v>
+      </c>
+      <c r="L28" t="s">
+        <v>259</v>
+      </c>
+      <c r="M28" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>261</v>
+      </c>
+      <c r="C29" t="s">
+        <v>262</v>
+      </c>
+      <c r="D29" t="s">
+        <v>263</v>
+      </c>
+      <c r="E29" t="s">
+        <v>264</v>
+      </c>
+      <c r="F29" t="s">
+        <v>265</v>
+      </c>
+      <c r="I29">
+        <v>28</v>
+      </c>
+      <c r="J29" t="s">
+        <v>261</v>
+      </c>
+      <c r="K29" t="s">
+        <v>262</v>
+      </c>
+      <c r="L29" t="s">
+        <v>263</v>
+      </c>
+      <c r="M29" t="s">
+        <v>264</v>
+      </c>
+      <c r="N29" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>267</v>
+      </c>
+      <c r="I30">
+        <v>29</v>
+      </c>
+      <c r="J30" t="s">
+        <v>275</v>
+      </c>
+      <c r="K30" t="s">
+        <v>268</v>
+      </c>
+      <c r="L30" t="s">
+        <v>269</v>
+      </c>
+      <c r="M30" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>266</v>
+      </c>
+      <c r="C31" t="s">
+        <v>268</v>
+      </c>
+      <c r="D31" t="s">
+        <v>269</v>
+      </c>
+      <c r="E31" t="s">
+        <v>270</v>
+      </c>
+      <c r="I31">
+        <v>30</v>
+      </c>
+      <c r="J31" t="s">
+        <v>267</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/syllabus/再構築計画.xlsx
+++ b/syllabus/再構築計画.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/napier/Dropbox/Git/psychometrtics_syllabus/syllabus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Napier/Dropbox/Git/psychometrtics_syllabus/syllabus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35C3CDE-B275-914B-8330-A0B8E817BA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C2D05F-6069-C24D-970D-37DC6E24E09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="1" xr2:uid="{5A83AC4D-FD37-C349-BFA0-5F3B00CCA608}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="291">
   <si>
     <t>16 確率と統計的推論</t>
   </si>
@@ -1832,12 +1832,60 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>標準化</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">ヒョウジュンカ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>標準化された差</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ヒョウジュンカ </t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t xml:space="preserve">サ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確率分布</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">カクリツブンプ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誤差と確率</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ゴサトカクリツ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>標準正規分布</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ヒョウジュンセイキブンプ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正規分布の別の意味</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">セイキブンプ </t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t xml:space="preserve">ベツノイミ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1877,12 +1925,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
@@ -1914,7 +1956,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1931,9 +1973,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2917,7 +2956,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAD22543-E06A-6249-A917-871CAD278F17}">
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="2" max="7" width="21" customWidth="1"/>
@@ -2928,7 +2967,7 @@
     <col min="14" max="14" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="B1" t="s">
         <v>130</v>
       </c>
@@ -2960,7 +2999,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2992,7 +3031,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3033,7 +3072,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="21">
+    <row r="4" spans="1:14" ht="21">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3071,7 +3110,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3109,7 +3148,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="21">
+    <row r="6" spans="1:14" ht="21">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3135,22 +3174,22 @@
         <v>5</v>
       </c>
       <c r="J6" t="s">
-        <v>283</v>
+        <v>150</v>
       </c>
       <c r="K6" t="s">
-        <v>284</v>
+        <v>151</v>
       </c>
       <c r="L6" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="M6" t="s">
-        <v>164</v>
+        <v>285</v>
       </c>
       <c r="N6" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3176,19 +3215,22 @@
         <v>6</v>
       </c>
       <c r="J7" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="K7" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="L7" t="s">
-        <v>281</v>
+        <v>162</v>
       </c>
       <c r="M7" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>164</v>
+      </c>
+      <c r="N7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3207,24 +3249,23 @@
       <c r="I8">
         <v>7</v>
       </c>
-      <c r="J8" t="s">
-        <v>279</v>
-      </c>
-      <c r="K8" t="s">
-        <v>280</v>
-      </c>
-      <c r="L8" t="s">
-        <v>176</v>
-      </c>
-      <c r="M8" t="s">
-        <v>177</v>
-      </c>
-      <c r="N8" t="s">
-        <v>178</v>
-      </c>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="J8" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3247,22 +3288,22 @@
         <v>8</v>
       </c>
       <c r="J9" t="s">
-        <v>180</v>
+        <v>277</v>
       </c>
       <c r="K9" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="L9" t="s">
-        <v>181</v>
+        <v>278</v>
       </c>
       <c r="M9" t="s">
-        <v>182</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>281</v>
+      </c>
+      <c r="N9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3285,22 +3326,22 @@
         <v>9</v>
       </c>
       <c r="J10" t="s">
-        <v>189</v>
+        <v>279</v>
       </c>
       <c r="K10" t="s">
-        <v>185</v>
+        <v>280</v>
       </c>
       <c r="L10" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="M10" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="N10" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3323,19 +3364,20 @@
         <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>166</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>167</v>
+        <v>180</v>
+      </c>
+      <c r="K11" t="s">
+        <v>179</v>
       </c>
       <c r="L11" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="M11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>182</v>
+      </c>
+      <c r="N11" s="5"/>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3361,22 +3403,22 @@
         <v>11</v>
       </c>
       <c r="J12" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="K12" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="L12" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="M12" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="N12" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3414,7 +3456,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:14">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3452,7 +3494,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:14">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3490,7 +3532,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:14">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3532,7 +3574,10 @@
       <c r="L17" t="s">
         <v>208</v>
       </c>
-      <c r="M17" t="s">
+      <c r="M17" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="N17" t="s">
         <v>209</v>
       </c>
     </row>

--- a/syllabus/再構築計画.xlsx
+++ b/syllabus/再構築計画.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Napier/Dropbox/Git/psychometrtics_syllabus/syllabus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/napier/Dropbox/Git/psychometrtics_syllabus/syllabus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C2D05F-6069-C24D-970D-37DC6E24E09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F38AC9-664B-424A-A748-78486AD93794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="1" xr2:uid="{5A83AC4D-FD37-C349-BFA0-5F3B00CCA608}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="293">
   <si>
     <t>16 確率と統計的推論</t>
   </si>
@@ -1880,12 +1880,29 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>偏回帰係数</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">ヘンカイキケイスウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部分相関と偏相関</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">ブブンソウカン </t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t xml:space="preserve">ヘンソウカン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1924,15 +1941,6 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1956,7 +1964,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1971,9 +1979,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3182,10 +3187,10 @@
       <c r="L6" t="s">
         <v>152</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="2" t="s">
         <v>286</v>
       </c>
     </row>
@@ -3293,13 +3298,13 @@
       <c r="K9" t="s">
         <v>154</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N9" s="2" t="s">
         <v>282</v>
       </c>
     </row>
@@ -3369,13 +3374,15 @@
       <c r="K11" t="s">
         <v>179</v>
       </c>
-      <c r="L11" t="s">
-        <v>181</v>
-      </c>
-      <c r="M11" t="s">
+      <c r="L11" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="N11" t="s">
         <v>182</v>
       </c>
-      <c r="N11" s="5"/>
     </row>
     <row r="12" spans="1:14">
       <c r="A12">

--- a/syllabus/再構築計画.xlsx
+++ b/syllabus/再構築計画.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/napier/Dropbox/Git/psychometrtics_syllabus/syllabus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F38AC9-664B-424A-A748-78486AD93794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7263B72B-EC20-8A40-B4D4-A97298DEF3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="1" xr2:uid="{5A83AC4D-FD37-C349-BFA0-5F3B00CCA608}"/>
+    <workbookView xWindow="27160" yWindow="660" windowWidth="20820" windowHeight="26600" activeTab="1" xr2:uid="{5A83AC4D-FD37-C349-BFA0-5F3B00CCA608}"/>
   </bookViews>
   <sheets>
     <sheet name="2021年後期" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="294">
   <si>
     <t>16 確率と統計的推論</t>
   </si>
@@ -1894,6 +1894,13 @@
     </rPh>
     <rPh sb="5" eb="8">
       <t xml:space="preserve">ヘンソウカン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>さまざまな交互作用</t>
+    <rPh sb="5" eb="9">
+      <t xml:space="preserve">コウゴサヨウ </t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3489,16 +3496,16 @@
         <v>195</v>
       </c>
       <c r="K14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N14" t="s">
-        <v>199</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -3536,7 +3543,7 @@
         <v>203</v>
       </c>
       <c r="N15" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:14">

--- a/syllabus/再構築計画.xlsx
+++ b/syllabus/再構築計画.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/napier/Dropbox/Git/psychometrtics_syllabus/syllabus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7263B72B-EC20-8A40-B4D4-A97298DEF3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B451D5-5451-A347-8D55-FD5983852380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27160" yWindow="660" windowWidth="20820" windowHeight="26600" activeTab="1" xr2:uid="{5A83AC4D-FD37-C349-BFA0-5F3B00CCA608}"/>
+    <workbookView xWindow="30280" yWindow="640" windowWidth="20820" windowHeight="26600" activeTab="1" xr2:uid="{5A83AC4D-FD37-C349-BFA0-5F3B00CCA608}"/>
   </bookViews>
   <sheets>
     <sheet name="2021年後期" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="294">
   <si>
     <t>16 確率と統計的推論</t>
   </si>
@@ -1898,9 +1898,9 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>さまざまな交互作用</t>
-    <rPh sb="5" eb="9">
-      <t xml:space="preserve">コウゴサヨウ </t>
+    <t>デザイン行列と混合モデル</t>
+    <rPh sb="7" eb="9">
+      <t xml:space="preserve">コンゴウ </t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3504,9 +3504,6 @@
       <c r="M14" t="s">
         <v>199</v>
       </c>
-      <c r="N14" t="s">
-        <v>293</v>
-      </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15">
@@ -3543,7 +3540,7 @@
         <v>203</v>
       </c>
       <c r="N15" t="s">
-        <v>196</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:14">
